--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_tarapaca.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.69402287276128</v>
+      </c>
+      <c r="C2">
         <v>27.14522045601669</v>
-      </c>
-      <c r="C2">
-        <v>27.69402287276128</v>
       </c>
       <c r="D2">
         <v>3.683889772125066</v>
       </c>
       <c r="E2">
-        <v>17.53122778982966</v>
+        <v>17.88566146242213</v>
       </c>
       <c r="F2">
         <v>64.58311074774821</v>
       </c>
       <c r="G2">
-        <v>17.88566146242213</v>
+        <v>17.53122778982966</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>36.67572964496441</v>
+      </c>
+      <c r="C3">
         <v>15.39164476133531</v>
-      </c>
-      <c r="C3">
-        <v>36.67572964496441</v>
       </c>
       <c r="D3">
         <v>6.497031444696914</v>
       </c>
       <c r="E3">
-        <v>10.12159565549629</v>
+        <v>24.11807910023666</v>
       </c>
       <c r="F3">
         <v>65.76032524426705</v>
       </c>
       <c r="G3">
-        <v>24.11807910023666</v>
+        <v>10.12159565549629</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>35.79692626489381</v>
+      </c>
+      <c r="C4">
         <v>23.4070108789501</v>
-      </c>
-      <c r="C4">
-        <v>35.79692626489381</v>
       </c>
       <c r="D4">
         <v>4.272224271486536</v>
       </c>
       <c r="E4">
-        <v>14.70253267530777</v>
+        <v>22.48495037691849</v>
       </c>
       <c r="F4">
         <v>62.81251694777373</v>
       </c>
       <c r="G4">
-        <v>22.48495037691849</v>
+        <v>14.70253267530777</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>45.13788098693759</v>
+      </c>
+      <c r="C5">
         <v>40.63860667634253</v>
-      </c>
-      <c r="C5">
-        <v>45.13788098693759</v>
       </c>
       <c r="D5">
         <v>2.460714285714286</v>
       </c>
       <c r="E5">
-        <v>21.875</v>
+        <v>24.296875</v>
       </c>
       <c r="F5">
         <v>53.82812499999999</v>
       </c>
       <c r="G5">
-        <v>24.296875</v>
+        <v>21.875</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>21.16868798235943</v>
+      </c>
+      <c r="C6">
         <v>24.14553472987872</v>
-      </c>
-      <c r="C6">
-        <v>21.16868798235943</v>
       </c>
       <c r="D6">
         <v>4.141552511415525</v>
       </c>
       <c r="E6">
-        <v>16.61608497723824</v>
+        <v>14.56752655538695</v>
       </c>
       <c r="F6">
         <v>68.81638846737481</v>
       </c>
       <c r="G6">
-        <v>14.56752655538695</v>
+        <v>16.61608497723824</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>48.20271066588096</v>
+      </c>
+      <c r="C7">
         <v>32.8815556865056</v>
-      </c>
-      <c r="C7">
-        <v>48.20271066588096</v>
       </c>
       <c r="D7">
         <v>3.041218637992832</v>
       </c>
       <c r="E7">
-        <v>18.15815164334526</v>
+        <v>26.61893914741295</v>
       </c>
       <c r="F7">
         <v>55.22290920924178</v>
       </c>
       <c r="G7">
-        <v>26.61893914741295</v>
+        <v>18.15815164334526</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>39.16243654822335</v>
+      </c>
+      <c r="C8">
         <v>35.71065989847716</v>
-      </c>
-      <c r="C8">
-        <v>39.16243654822335</v>
       </c>
       <c r="D8">
         <v>2.800284292821606</v>
       </c>
       <c r="E8">
-        <v>20.42089985486212</v>
+        <v>22.39477503628447</v>
       </c>
       <c r="F8">
         <v>57.18432510885341</v>
       </c>
       <c r="G8">
-        <v>22.39477503628447</v>
+        <v>20.42089985486212</v>
       </c>
     </row>
   </sheetData>
